--- a/packages/to-excel/out1/组件总表（PC+ElementPlus）-合并.xlsx
+++ b/packages/to-excel/out1/组件总表（PC+ElementPlus）-合并.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31895" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31802" uniqueCount="827">
   <si>
     <t>子组件名称</t>
   </si>
@@ -2246,7 +2246,13 @@
     <t>startDate</t>
   </si>
   <si>
+    <t>startValue</t>
+  </si>
+  <si>
     <t>endDate</t>
+  </si>
+  <si>
+    <t>endValue</t>
   </si>
   <si>
     <t>yearDiff</t>
@@ -2261,7 +2267,13 @@
     <t>placeholderRight</t>
   </si>
   <si>
+    <t>endPlaceholder</t>
+  </si>
+  <si>
     <t>preIcon</t>
+  </si>
+  <si>
+    <t>prefixIconName</t>
   </si>
   <si>
     <t>UTimePicker</t>
@@ -2277,9 +2289,6 @@
   </si>
   <si>
     <t>minUnit</t>
-  </si>
-  <si>
-    <t>isRange</t>
   </si>
   <si>
     <t>startTime</t>
@@ -2511,7 +2520,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2529,13 +2538,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3040,13 +3042,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3055,118 +3060,115 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3181,8 +3183,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -86970,7 +86972,7 @@
       <c r="E1530" t="s">
         <v>737</v>
       </c>
-      <c r="F1530"/>
+      <c r="F1530" s="4"/>
       <c r="G1530" t="s">
         <v>22</v>
       </c>
@@ -87020,7 +87022,7 @@
       <c r="E1531" t="s">
         <v>571</v>
       </c>
-      <c r="F1531"/>
+      <c r="F1531" s="4"/>
       <c r="G1531" t="s">
         <v>22</v>
       </c>
@@ -87122,7 +87124,9 @@
       <c r="E1533" t="s">
         <v>738</v>
       </c>
-      <c r="F1533"/>
+      <c r="F1533" s="8" t="s">
+        <v>739</v>
+      </c>
       <c r="G1533" t="s">
         <v>22</v>
       </c>
@@ -87170,9 +87174,11 @@
       </c>
       <c r="D1534"/>
       <c r="E1534" t="s">
-        <v>739</v>
-      </c>
-      <c r="F1534"/>
+        <v>740</v>
+      </c>
+      <c r="F1534" s="8" t="s">
+        <v>741</v>
+      </c>
       <c r="G1534" t="s">
         <v>22</v>
       </c>
@@ -87222,7 +87228,7 @@
       <c r="E1535" t="s">
         <v>440</v>
       </c>
-      <c r="F1535"/>
+      <c r="F1535" s="4"/>
       <c r="G1535" t="s">
         <v>22</v>
       </c>
@@ -87272,7 +87278,7 @@
       <c r="E1536" t="s">
         <v>441</v>
       </c>
-      <c r="F1536"/>
+      <c r="F1536" s="4"/>
       <c r="G1536" t="s">
         <v>22</v>
       </c>
@@ -87320,9 +87326,9 @@
       </c>
       <c r="D1537"/>
       <c r="E1537" t="s">
-        <v>740</v>
-      </c>
-      <c r="F1537"/>
+        <v>742</v>
+      </c>
+      <c r="F1537" s="4"/>
       <c r="G1537" t="s">
         <v>22</v>
       </c>
@@ -87370,9 +87376,9 @@
       </c>
       <c r="D1538"/>
       <c r="E1538" t="s">
-        <v>741</v>
-      </c>
-      <c r="F1538"/>
+        <v>743</v>
+      </c>
+      <c r="F1538" s="4"/>
       <c r="G1538" t="s">
         <v>22</v>
       </c>
@@ -87422,7 +87428,7 @@
       <c r="E1539" t="s">
         <v>512</v>
       </c>
-      <c r="F1539"/>
+      <c r="F1539" s="4"/>
       <c r="G1539" t="s">
         <v>22</v>
       </c>
@@ -87472,7 +87478,7 @@
       <c r="E1540" t="s">
         <v>513</v>
       </c>
-      <c r="F1540"/>
+      <c r="F1540" s="4"/>
       <c r="G1540" t="s">
         <v>22</v>
       </c>
@@ -87520,9 +87526,9 @@
       </c>
       <c r="D1541"/>
       <c r="E1541" t="s">
-        <v>742</v>
-      </c>
-      <c r="F1541"/>
+        <v>744</v>
+      </c>
+      <c r="F1541" s="4"/>
       <c r="G1541" t="s">
         <v>22</v>
       </c>
@@ -87572,7 +87578,7 @@
       <c r="E1542" t="s">
         <v>487</v>
       </c>
-      <c r="F1542"/>
+      <c r="F1542" s="4"/>
       <c r="G1542" t="s">
         <v>22</v>
       </c>
@@ -87622,7 +87628,9 @@
       <c r="E1543" t="s">
         <v>427</v>
       </c>
-      <c r="F1543"/>
+      <c r="F1543" t="s">
+        <v>427</v>
+      </c>
       <c r="G1543" t="s">
         <v>22</v>
       </c>
@@ -87670,9 +87678,11 @@
       </c>
       <c r="D1544"/>
       <c r="E1544" t="s">
-        <v>743</v>
-      </c>
-      <c r="F1544"/>
+        <v>745</v>
+      </c>
+      <c r="F1544" s="8" t="s">
+        <v>746</v>
+      </c>
       <c r="G1544" t="s">
         <v>22</v>
       </c>
@@ -87722,7 +87732,7 @@
       <c r="E1545" t="s">
         <v>25</v>
       </c>
-      <c r="F1545"/>
+      <c r="F1545" s="4"/>
       <c r="G1545" t="s">
         <v>22</v>
       </c>
@@ -87772,7 +87782,7 @@
       <c r="E1546" t="s">
         <v>544</v>
       </c>
-      <c r="F1546"/>
+      <c r="F1546" s="4"/>
       <c r="G1546" t="s">
         <v>22</v>
       </c>
@@ -87820,9 +87830,11 @@
       </c>
       <c r="D1547"/>
       <c r="E1547" t="s">
-        <v>744</v>
-      </c>
-      <c r="F1547"/>
+        <v>747</v>
+      </c>
+      <c r="F1547" t="s">
+        <v>748</v>
+      </c>
       <c r="G1547" t="s">
         <v>22</v>
       </c>
@@ -87872,7 +87884,7 @@
       <c r="E1548" t="s">
         <v>491</v>
       </c>
-      <c r="F1548"/>
+      <c r="F1548" s="4"/>
       <c r="G1548" t="s">
         <v>22</v>
       </c>
@@ -87922,7 +87934,9 @@
       <c r="E1549" t="s">
         <v>151</v>
       </c>
-      <c r="F1549"/>
+      <c r="F1549" s="8" t="s">
+        <v>152</v>
+      </c>
       <c r="G1549" t="s">
         <v>22</v>
       </c>
@@ -87972,7 +87986,9 @@
       <c r="E1550" t="s">
         <v>429</v>
       </c>
-      <c r="F1550"/>
+      <c r="F1550" t="s">
+        <v>429</v>
+      </c>
       <c r="G1550" t="s">
         <v>22</v>
       </c>
@@ -88022,7 +88038,7 @@
       <c r="E1551" t="s">
         <v>485</v>
       </c>
-      <c r="F1551"/>
+      <c r="F1551" s="4"/>
       <c r="G1551" t="s">
         <v>22</v>
       </c>
@@ -88072,7 +88088,9 @@
       <c r="E1552" t="s">
         <v>106</v>
       </c>
-      <c r="F1552"/>
+      <c r="F1552" t="s">
+        <v>106</v>
+      </c>
       <c r="G1552" t="s">
         <v>22</v>
       </c>
@@ -88122,7 +88140,9 @@
       <c r="E1553" t="s">
         <v>79</v>
       </c>
-      <c r="F1553"/>
+      <c r="F1553" t="s">
+        <v>79</v>
+      </c>
       <c r="G1553" t="s">
         <v>22</v>
       </c>
@@ -88172,7 +88192,7 @@
       <c r="E1554" t="s">
         <v>275</v>
       </c>
-      <c r="F1554"/>
+      <c r="F1554" s="4"/>
       <c r="G1554" t="s">
         <v>22</v>
       </c>
@@ -88222,7 +88242,7 @@
       <c r="E1555" t="s">
         <v>153</v>
       </c>
-      <c r="F1555"/>
+      <c r="F1555" s="4"/>
       <c r="G1555" t="s">
         <v>22</v>
       </c>
@@ -88272,7 +88292,9 @@
       <c r="E1556" t="s">
         <v>194</v>
       </c>
-      <c r="F1556"/>
+      <c r="F1556" s="8" t="s">
+        <v>206</v>
+      </c>
       <c r="G1556" t="s">
         <v>22</v>
       </c>
@@ -88322,7 +88344,9 @@
       <c r="E1557" t="s">
         <v>431</v>
       </c>
-      <c r="F1557"/>
+      <c r="F1557" s="8" t="s">
+        <v>206</v>
+      </c>
       <c r="G1557" t="s">
         <v>22</v>
       </c>
@@ -88377,7 +88401,7 @@
         <v>96</v>
       </c>
       <c r="H1558" t="s">
-        <v>22</v>
+        <v>484</v>
       </c>
       <c r="I1558" t="s">
         <v>22</v>
@@ -88426,8 +88450,8 @@
       <c r="G1559" t="s">
         <v>738</v>
       </c>
-      <c r="H1559" t="s">
-        <v>22</v>
+      <c r="H1559" s="8" t="s">
+        <v>739</v>
       </c>
       <c r="I1559" t="s">
         <v>22</v>
@@ -88474,10 +88498,10 @@
       </c>
       <c r="F1560"/>
       <c r="G1560" t="s">
-        <v>739</v>
-      </c>
-      <c r="H1560" t="s">
-        <v>22</v>
+        <v>740</v>
+      </c>
+      <c r="H1560" s="8" t="s">
+        <v>741</v>
       </c>
       <c r="I1560" t="s">
         <v>22</v>
@@ -88526,7 +88550,7 @@
       <c r="G1561" t="s">
         <v>79</v>
       </c>
-      <c r="H1561" t="s">
+      <c r="H1561" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I1561" t="s">
@@ -88576,7 +88600,7 @@
       <c r="G1562" t="s">
         <v>106</v>
       </c>
-      <c r="H1562" t="s">
+      <c r="H1562" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I1562" t="s">
@@ -88626,7 +88650,7 @@
       <c r="G1563" t="s">
         <v>275</v>
       </c>
-      <c r="H1563" t="s">
+      <c r="H1563" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I1563" t="s">
@@ -88676,7 +88700,7 @@
       <c r="G1564" t="s">
         <v>153</v>
       </c>
-      <c r="H1564" t="s">
+      <c r="H1564" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I1564" t="s">
@@ -88732,7 +88756,7 @@
       <c r="I1565" t="s">
         <v>124</v>
       </c>
-      <c r="J1565" t="s">
+      <c r="J1565" s="4" t="s">
         <v>22</v>
       </c>
       <c r="K1565" t="s">
@@ -88783,7 +88807,7 @@
         <v>125</v>
       </c>
       <c r="J1566" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="K1566" t="s">
         <v>22</v>
@@ -88832,7 +88856,7 @@
       <c r="I1567" t="s">
         <v>108</v>
       </c>
-      <c r="J1567" t="s">
+      <c r="J1567" s="4" t="s">
         <v>22</v>
       </c>
       <c r="K1567" t="s">
@@ -88882,9 +88906,7 @@
       <c r="I1568" t="s">
         <v>480</v>
       </c>
-      <c r="J1568" t="s">
-        <v>22</v>
-      </c>
+      <c r="J1568" s="4"/>
       <c r="K1568" t="s">
         <v>22</v>
       </c>
@@ -88933,7 +88955,7 @@
         <v>81</v>
       </c>
       <c r="J1569" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="K1569" t="s">
         <v>22</v>
@@ -88962,23 +88984,21 @@
     </row>
     <row r="1570" spans="1:18">
       <c r="A1570" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B1570" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="C1570" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="D1570" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="E1570" t="s">
-        <v>749</v>
-      </c>
-      <c r="F1570" t="s">
-        <v>750</v>
-      </c>
+        <v>753</v>
+      </c>
+      <c r="F1570"/>
       <c r="G1570" t="s">
         <v>22</v>
       </c>
@@ -89018,23 +89038,17 @@
     </row>
     <row r="1571" spans="1:18">
       <c r="A1571" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1571" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1571"/>
       <c r="C1571" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1571" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1571"/>
       <c r="E1571" t="s">
         <v>571</v>
       </c>
-      <c r="F1571" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1571"/>
       <c r="G1571" t="s">
         <v>22</v>
       </c>
@@ -89074,23 +89088,17 @@
     </row>
     <row r="1572" spans="1:18">
       <c r="A1572" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1572" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1572"/>
       <c r="C1572" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1572" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1572"/>
       <c r="E1572" t="s">
         <v>427</v>
       </c>
-      <c r="F1572" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1572"/>
       <c r="G1572" t="s">
         <v>22</v>
       </c>
@@ -89130,23 +89138,17 @@
     </row>
     <row r="1573" spans="1:18">
       <c r="A1573" t="s">
+        <v>749</v>
+      </c>
+      <c r="B1573"/>
+      <c r="C1573" t="s">
+        <v>751</v>
+      </c>
+      <c r="D1573"/>
+      <c r="E1573" t="s">
         <v>745</v>
       </c>
-      <c r="B1573" t="s">
-        <v>746</v>
-      </c>
-      <c r="C1573" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1573" t="s">
-        <v>748</v>
-      </c>
-      <c r="E1573" t="s">
-        <v>743</v>
-      </c>
-      <c r="F1573" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1573"/>
       <c r="G1573" t="s">
         <v>22</v>
       </c>
@@ -89186,23 +89188,17 @@
     </row>
     <row r="1574" spans="1:18">
       <c r="A1574" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1574" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1574"/>
       <c r="C1574" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1574" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1574"/>
       <c r="E1574" t="s">
         <v>96</v>
       </c>
-      <c r="F1574" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1574"/>
       <c r="G1574" t="s">
         <v>22</v>
       </c>
@@ -89242,23 +89238,17 @@
     </row>
     <row r="1575" spans="1:18">
       <c r="A1575" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1575" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1575"/>
       <c r="C1575" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1575" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1575"/>
       <c r="E1575" t="s">
-        <v>751</v>
-      </c>
-      <c r="F1575" t="s">
-        <v>750</v>
-      </c>
+        <v>754</v>
+      </c>
+      <c r="F1575"/>
       <c r="G1575" t="s">
         <v>22</v>
       </c>
@@ -89298,23 +89288,17 @@
     </row>
     <row r="1576" spans="1:18">
       <c r="A1576" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1576" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1576"/>
       <c r="C1576" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1576" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1576"/>
       <c r="E1576" t="s">
-        <v>752</v>
-      </c>
-      <c r="F1576" t="s">
-        <v>750</v>
-      </c>
+        <v>755</v>
+      </c>
+      <c r="F1576"/>
       <c r="G1576" t="s">
         <v>22</v>
       </c>
@@ -89354,23 +89338,17 @@
     </row>
     <row r="1577" spans="1:18">
       <c r="A1577" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1577" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1577"/>
       <c r="C1577" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1577" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1577"/>
       <c r="E1577" t="s">
-        <v>753</v>
-      </c>
-      <c r="F1577" t="s">
-        <v>750</v>
-      </c>
+        <v>756</v>
+      </c>
+      <c r="F1577"/>
       <c r="G1577" t="s">
         <v>22</v>
       </c>
@@ -89410,23 +89388,17 @@
     </row>
     <row r="1578" spans="1:18">
       <c r="A1578" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1578" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1578"/>
       <c r="C1578" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1578" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1578"/>
       <c r="E1578" t="s">
-        <v>754</v>
-      </c>
-      <c r="F1578" t="s">
-        <v>750</v>
-      </c>
+        <v>757</v>
+      </c>
+      <c r="F1578"/>
       <c r="G1578" t="s">
         <v>22</v>
       </c>
@@ -89466,23 +89438,17 @@
     </row>
     <row r="1579" spans="1:18">
       <c r="A1579" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1579" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1579"/>
       <c r="C1579" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1579" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1579"/>
       <c r="E1579" t="s">
-        <v>742</v>
-      </c>
-      <c r="F1579" t="s">
-        <v>750</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="F1579"/>
       <c r="G1579" t="s">
         <v>22</v>
       </c>
@@ -89522,23 +89488,17 @@
     </row>
     <row r="1580" spans="1:18">
       <c r="A1580" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1580" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1580"/>
       <c r="C1580" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1580" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1580"/>
       <c r="E1580" t="s">
         <v>512</v>
       </c>
-      <c r="F1580" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1580"/>
       <c r="G1580" t="s">
         <v>22</v>
       </c>
@@ -89578,23 +89538,17 @@
     </row>
     <row r="1581" spans="1:18">
       <c r="A1581" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1581" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1581"/>
       <c r="C1581" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1581" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1581"/>
       <c r="E1581" t="s">
         <v>513</v>
       </c>
-      <c r="F1581" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1581"/>
       <c r="G1581" t="s">
         <v>22</v>
       </c>
@@ -89634,23 +89588,17 @@
     </row>
     <row r="1582" spans="1:18">
       <c r="A1582" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1582" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1582"/>
       <c r="C1582" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1582" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1582"/>
       <c r="E1582" t="s">
         <v>487</v>
       </c>
-      <c r="F1582" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1582"/>
       <c r="G1582" t="s">
         <v>22</v>
       </c>
@@ -89690,23 +89638,17 @@
     </row>
     <row r="1583" spans="1:18">
       <c r="A1583" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1583" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1583"/>
       <c r="C1583" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1583" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1583"/>
       <c r="E1583" t="s">
-        <v>755</v>
-      </c>
-      <c r="F1583" t="s">
-        <v>750</v>
-      </c>
+        <v>758</v>
+      </c>
+      <c r="F1583"/>
       <c r="G1583" t="s">
         <v>22</v>
       </c>
@@ -89746,23 +89688,17 @@
     </row>
     <row r="1584" spans="1:18">
       <c r="A1584" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1584" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1584"/>
       <c r="C1584" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1584" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1584"/>
       <c r="E1584" t="s">
-        <v>756</v>
-      </c>
-      <c r="F1584" t="s">
-        <v>750</v>
-      </c>
+        <v>759</v>
+      </c>
+      <c r="F1584"/>
       <c r="G1584" t="s">
         <v>22</v>
       </c>
@@ -89802,23 +89738,17 @@
     </row>
     <row r="1585" spans="1:18">
       <c r="A1585" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1585" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1585"/>
       <c r="C1585" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1585" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1585"/>
       <c r="E1585" t="s">
-        <v>757</v>
-      </c>
-      <c r="F1585" t="s">
-        <v>750</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="F1585"/>
       <c r="G1585" t="s">
         <v>22</v>
       </c>
@@ -89858,23 +89788,17 @@
     </row>
     <row r="1586" spans="1:18">
       <c r="A1586" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1586" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1586"/>
       <c r="C1586" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1586" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1586"/>
       <c r="E1586" t="s">
-        <v>758</v>
-      </c>
-      <c r="F1586" t="s">
-        <v>750</v>
-      </c>
+        <v>761</v>
+      </c>
+      <c r="F1586"/>
       <c r="G1586" t="s">
         <v>22</v>
       </c>
@@ -89914,23 +89838,17 @@
     </row>
     <row r="1587" spans="1:18">
       <c r="A1587" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1587" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1587"/>
       <c r="C1587" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1587" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1587"/>
       <c r="E1587" t="s">
-        <v>759</v>
-      </c>
-      <c r="F1587" t="s">
-        <v>750</v>
-      </c>
+        <v>762</v>
+      </c>
+      <c r="F1587"/>
       <c r="G1587" t="s">
         <v>22</v>
       </c>
@@ -89970,23 +89888,17 @@
     </row>
     <row r="1588" spans="1:18">
       <c r="A1588" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1588" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1588"/>
       <c r="C1588" t="s">
+        <v>751</v>
+      </c>
+      <c r="D1588"/>
+      <c r="E1588" t="s">
         <v>747</v>
       </c>
-      <c r="D1588" t="s">
-        <v>748</v>
-      </c>
-      <c r="E1588" t="s">
-        <v>744</v>
-      </c>
-      <c r="F1588" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1588"/>
       <c r="G1588" t="s">
         <v>22</v>
       </c>
@@ -90026,23 +89938,17 @@
     </row>
     <row r="1589" spans="1:18">
       <c r="A1589" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1589" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1589"/>
       <c r="C1589" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1589" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1589"/>
       <c r="E1589" t="s">
         <v>491</v>
       </c>
-      <c r="F1589" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1589"/>
       <c r="G1589" t="s">
         <v>22</v>
       </c>
@@ -90082,23 +89988,17 @@
     </row>
     <row r="1590" spans="1:18">
       <c r="A1590" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1590" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1590"/>
       <c r="C1590" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1590" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1590"/>
       <c r="E1590" t="s">
         <v>151</v>
       </c>
-      <c r="F1590" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1590"/>
       <c r="G1590" t="s">
         <v>22</v>
       </c>
@@ -90138,23 +90038,17 @@
     </row>
     <row r="1591" spans="1:18">
       <c r="A1591" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1591" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1591"/>
       <c r="C1591" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1591" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1591"/>
       <c r="E1591" t="s">
         <v>429</v>
       </c>
-      <c r="F1591" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1591"/>
       <c r="G1591" t="s">
         <v>22</v>
       </c>
@@ -90194,23 +90088,17 @@
     </row>
     <row r="1592" spans="1:18">
       <c r="A1592" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1592" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1592"/>
       <c r="C1592" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1592" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1592"/>
       <c r="E1592" t="s">
         <v>106</v>
       </c>
-      <c r="F1592" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1592"/>
       <c r="G1592" t="s">
         <v>22</v>
       </c>
@@ -90250,23 +90138,17 @@
     </row>
     <row r="1593" spans="1:18">
       <c r="A1593" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1593" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1593"/>
       <c r="C1593" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1593" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1593"/>
       <c r="E1593" t="s">
         <v>79</v>
       </c>
-      <c r="F1593" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1593"/>
       <c r="G1593" t="s">
         <v>22</v>
       </c>
@@ -90306,23 +90188,17 @@
     </row>
     <row r="1594" spans="1:18">
       <c r="A1594" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1594" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1594"/>
       <c r="C1594" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1594" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1594"/>
       <c r="E1594" t="s">
         <v>275</v>
       </c>
-      <c r="F1594" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1594"/>
       <c r="G1594" t="s">
         <v>22</v>
       </c>
@@ -90362,23 +90238,17 @@
     </row>
     <row r="1595" spans="1:18">
       <c r="A1595" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1595" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1595"/>
       <c r="C1595" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1595" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1595"/>
       <c r="E1595" t="s">
         <v>194</v>
       </c>
-      <c r="F1595" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1595"/>
       <c r="G1595" t="s">
         <v>22</v>
       </c>
@@ -90418,23 +90288,17 @@
     </row>
     <row r="1596" spans="1:18">
       <c r="A1596" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1596" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1596"/>
       <c r="C1596" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1596" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1596"/>
       <c r="E1596" t="s">
         <v>431</v>
       </c>
-      <c r="F1596" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1596"/>
       <c r="G1596" t="s">
         <v>22</v>
       </c>
@@ -90474,23 +90338,17 @@
     </row>
     <row r="1597" spans="1:18">
       <c r="A1597" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1597" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1597"/>
       <c r="C1597" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1597" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1597"/>
       <c r="E1597" t="s">
         <v>22</v>
       </c>
-      <c r="F1597" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1597"/>
       <c r="G1597" t="s">
         <v>96</v>
       </c>
@@ -90530,25 +90388,19 @@
     </row>
     <row r="1598" spans="1:18">
       <c r="A1598" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1598" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1598"/>
       <c r="C1598" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1598" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1598"/>
       <c r="E1598" t="s">
         <v>22</v>
       </c>
-      <c r="F1598" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1598"/>
       <c r="G1598" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H1598" t="s">
         <v>22</v>
@@ -90586,25 +90438,19 @@
     </row>
     <row r="1599" spans="1:18">
       <c r="A1599" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1599" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1599"/>
       <c r="C1599" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1599" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1599"/>
       <c r="E1599" t="s">
         <v>22</v>
       </c>
-      <c r="F1599" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1599"/>
       <c r="G1599" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="H1599" t="s">
         <v>22</v>
@@ -90642,23 +90488,17 @@
     </row>
     <row r="1600" spans="1:18">
       <c r="A1600" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1600" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1600"/>
       <c r="C1600" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1600" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1600"/>
       <c r="E1600" t="s">
         <v>22</v>
       </c>
-      <c r="F1600" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1600"/>
       <c r="G1600" t="s">
         <v>79</v>
       </c>
@@ -90698,23 +90538,17 @@
     </row>
     <row r="1601" spans="1:18">
       <c r="A1601" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1601" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1601"/>
       <c r="C1601" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1601" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1601"/>
       <c r="E1601" t="s">
         <v>22</v>
       </c>
-      <c r="F1601" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1601"/>
       <c r="G1601" t="s">
         <v>106</v>
       </c>
@@ -90754,23 +90588,17 @@
     </row>
     <row r="1602" spans="1:18">
       <c r="A1602" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1602" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1602"/>
       <c r="C1602" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1602" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1602"/>
       <c r="E1602" t="s">
         <v>22</v>
       </c>
-      <c r="F1602" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1602"/>
       <c r="G1602" t="s">
         <v>275</v>
       </c>
@@ -90810,23 +90638,17 @@
     </row>
     <row r="1603" spans="1:18">
       <c r="A1603" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1603" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1603"/>
       <c r="C1603" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1603" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1603"/>
       <c r="E1603" t="s">
         <v>22</v>
       </c>
-      <c r="F1603" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1603"/>
       <c r="G1603" t="s">
         <v>22</v>
       </c>
@@ -90866,23 +90688,17 @@
     </row>
     <row r="1604" spans="1:18">
       <c r="A1604" t="s">
-        <v>745</v>
-      </c>
-      <c r="B1604" t="s">
-        <v>746</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="B1604"/>
       <c r="C1604" t="s">
-        <v>747</v>
-      </c>
-      <c r="D1604" t="s">
-        <v>748</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="D1604"/>
       <c r="E1604" t="s">
         <v>22</v>
       </c>
-      <c r="F1604" t="s">
-        <v>750</v>
-      </c>
+      <c r="F1604"/>
       <c r="G1604" t="s">
         <v>22</v>
       </c>
@@ -90922,19 +90738,19 @@
     </row>
     <row r="1605" spans="1:18">
       <c r="A1605" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1605" t="s">
         <v>22</v>
       </c>
       <c r="C1605" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1605" t="s">
         <v>22</v>
       </c>
       <c r="E1605" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="F1605" t="s">
         <v>22</v>
@@ -90978,13 +90794,13 @@
     </row>
     <row r="1606" spans="1:18">
       <c r="A1606" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1606" t="s">
         <v>22</v>
       </c>
       <c r="C1606" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1606" t="s">
         <v>22</v>
@@ -91034,13 +90850,13 @@
     </row>
     <row r="1607" spans="1:18">
       <c r="A1607" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1607" t="s">
         <v>22</v>
       </c>
       <c r="C1607" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1607" t="s">
         <v>22</v>
@@ -91090,13 +90906,13 @@
     </row>
     <row r="1608" spans="1:18">
       <c r="A1608" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1608" t="s">
         <v>22</v>
       </c>
       <c r="C1608" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1608" t="s">
         <v>22</v>
@@ -91146,19 +90962,19 @@
     </row>
     <row r="1609" spans="1:18">
       <c r="A1609" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1609" t="s">
         <v>22</v>
       </c>
       <c r="C1609" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1609" t="s">
         <v>22</v>
       </c>
       <c r="E1609" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F1609" t="s">
         <v>22</v>
@@ -91202,13 +91018,13 @@
     </row>
     <row r="1610" spans="1:18">
       <c r="A1610" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1610" t="s">
         <v>22</v>
       </c>
       <c r="C1610" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1610" t="s">
         <v>22</v>
@@ -91258,13 +91074,13 @@
     </row>
     <row r="1611" spans="1:18">
       <c r="A1611" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1611" t="s">
         <v>22</v>
       </c>
       <c r="C1611" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1611" t="s">
         <v>22</v>
@@ -91314,19 +91130,19 @@
     </row>
     <row r="1612" spans="1:18">
       <c r="A1612" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1612" t="s">
         <v>22</v>
       </c>
       <c r="C1612" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1612" t="s">
         <v>22</v>
       </c>
       <c r="E1612" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="F1612" t="s">
         <v>22</v>
@@ -91370,19 +91186,19 @@
     </row>
     <row r="1613" spans="1:18">
       <c r="A1613" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1613" t="s">
         <v>22</v>
       </c>
       <c r="C1613" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1613" t="s">
         <v>22</v>
       </c>
       <c r="E1613" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F1613" t="s">
         <v>22</v>
@@ -91426,19 +91242,19 @@
     </row>
     <row r="1614" spans="1:18">
       <c r="A1614" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1614" t="s">
         <v>22</v>
       </c>
       <c r="C1614" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1614" t="s">
         <v>22</v>
       </c>
       <c r="E1614" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="F1614" t="s">
         <v>22</v>
@@ -91482,19 +91298,19 @@
     </row>
     <row r="1615" spans="1:18">
       <c r="A1615" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1615" t="s">
         <v>22</v>
       </c>
       <c r="C1615" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1615" t="s">
         <v>22</v>
       </c>
       <c r="E1615" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="F1615" t="s">
         <v>22</v>
@@ -91538,13 +91354,13 @@
     </row>
     <row r="1616" spans="1:18">
       <c r="A1616" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1616" t="s">
         <v>22</v>
       </c>
       <c r="C1616" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1616" t="s">
         <v>22</v>
@@ -91594,13 +91410,13 @@
     </row>
     <row r="1617" spans="1:18">
       <c r="A1617" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1617" t="s">
         <v>22</v>
       </c>
       <c r="C1617" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1617" t="s">
         <v>22</v>
@@ -91650,13 +91466,13 @@
     </row>
     <row r="1618" spans="1:18">
       <c r="A1618" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1618" t="s">
         <v>22</v>
       </c>
       <c r="C1618" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1618" t="s">
         <v>22</v>
@@ -91706,19 +91522,19 @@
     </row>
     <row r="1619" spans="1:18">
       <c r="A1619" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1619" t="s">
         <v>22</v>
       </c>
       <c r="C1619" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1619" t="s">
         <v>22</v>
       </c>
       <c r="E1619" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="F1619" t="s">
         <v>22</v>
@@ -91762,13 +91578,13 @@
     </row>
     <row r="1620" spans="1:18">
       <c r="A1620" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1620" t="s">
         <v>22</v>
       </c>
       <c r="C1620" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1620" t="s">
         <v>22</v>
@@ -91818,19 +91634,19 @@
     </row>
     <row r="1621" spans="1:18">
       <c r="A1621" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1621" t="s">
         <v>22</v>
       </c>
       <c r="C1621" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1621" t="s">
         <v>22</v>
       </c>
       <c r="E1621" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="F1621" t="s">
         <v>22</v>
@@ -91874,19 +91690,19 @@
     </row>
     <row r="1622" spans="1:18">
       <c r="A1622" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1622" t="s">
         <v>22</v>
       </c>
       <c r="C1622" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1622" t="s">
         <v>22</v>
       </c>
       <c r="E1622" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="F1622" t="s">
         <v>22</v>
@@ -91930,19 +91746,19 @@
     </row>
     <row r="1623" spans="1:18">
       <c r="A1623" t="s">
+        <v>763</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>764</v>
+      </c>
+      <c r="D1623" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1623" t="s">
         <v>760</v>
-      </c>
-      <c r="B1623" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1623" t="s">
-        <v>761</v>
-      </c>
-      <c r="D1623" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1623" t="s">
-        <v>757</v>
       </c>
       <c r="F1623" t="s">
         <v>22</v>
@@ -91986,19 +91802,19 @@
     </row>
     <row r="1624" spans="1:18">
       <c r="A1624" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1624" t="s">
         <v>22</v>
       </c>
       <c r="C1624" t="s">
+        <v>764</v>
+      </c>
+      <c r="D1624" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1624" t="s">
         <v>761</v>
-      </c>
-      <c r="D1624" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1624" t="s">
-        <v>758</v>
       </c>
       <c r="F1624" t="s">
         <v>22</v>
@@ -92042,19 +91858,19 @@
     </row>
     <row r="1625" spans="1:18">
       <c r="A1625" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1625" t="s">
         <v>22</v>
       </c>
       <c r="C1625" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1625" t="s">
         <v>22</v>
       </c>
       <c r="E1625" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="F1625" t="s">
         <v>22</v>
@@ -92098,13 +91914,13 @@
     </row>
     <row r="1626" spans="1:18">
       <c r="A1626" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1626" t="s">
         <v>22</v>
       </c>
       <c r="C1626" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1626" t="s">
         <v>22</v>
@@ -92154,19 +91970,19 @@
     </row>
     <row r="1627" spans="1:18">
       <c r="A1627" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1627" t="s">
         <v>22</v>
       </c>
       <c r="C1627" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1627" t="s">
         <v>22</v>
       </c>
       <c r="E1627" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="F1627" t="s">
         <v>22</v>
@@ -92210,13 +92026,13 @@
     </row>
     <row r="1628" spans="1:18">
       <c r="A1628" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1628" t="s">
         <v>22</v>
       </c>
       <c r="C1628" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1628" t="s">
         <v>22</v>
@@ -92266,13 +92082,13 @@
     </row>
     <row r="1629" spans="1:18">
       <c r="A1629" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1629" t="s">
         <v>22</v>
       </c>
       <c r="C1629" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1629" t="s">
         <v>22</v>
@@ -92322,13 +92138,13 @@
     </row>
     <row r="1630" spans="1:18">
       <c r="A1630" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1630" t="s">
         <v>22</v>
       </c>
       <c r="C1630" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1630" t="s">
         <v>22</v>
@@ -92378,13 +92194,13 @@
     </row>
     <row r="1631" spans="1:18">
       <c r="A1631" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1631" t="s">
         <v>22</v>
       </c>
       <c r="C1631" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1631" t="s">
         <v>22</v>
@@ -92434,13 +92250,13 @@
     </row>
     <row r="1632" spans="1:18">
       <c r="A1632" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1632" t="s">
         <v>22</v>
       </c>
       <c r="C1632" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1632" t="s">
         <v>22</v>
@@ -92490,13 +92306,13 @@
     </row>
     <row r="1633" spans="1:18">
       <c r="A1633" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1633" t="s">
         <v>22</v>
       </c>
       <c r="C1633" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1633" t="s">
         <v>22</v>
@@ -92546,13 +92362,13 @@
     </row>
     <row r="1634" spans="1:18">
       <c r="A1634" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1634" t="s">
         <v>22</v>
       </c>
       <c r="C1634" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1634" t="s">
         <v>22</v>
@@ -92602,13 +92418,13 @@
     </row>
     <row r="1635" spans="1:18">
       <c r="A1635" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1635" t="s">
         <v>22</v>
       </c>
       <c r="C1635" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1635" t="s">
         <v>22</v>
@@ -92658,13 +92474,13 @@
     </row>
     <row r="1636" spans="1:18">
       <c r="A1636" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1636" t="s">
         <v>22</v>
       </c>
       <c r="C1636" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1636" t="s">
         <v>22</v>
@@ -92714,13 +92530,13 @@
     </row>
     <row r="1637" spans="1:18">
       <c r="A1637" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1637" t="s">
         <v>22</v>
       </c>
       <c r="C1637" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1637" t="s">
         <v>22</v>
@@ -92770,13 +92586,13 @@
     </row>
     <row r="1638" spans="1:18">
       <c r="A1638" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1638" t="s">
         <v>22</v>
       </c>
       <c r="C1638" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1638" t="s">
         <v>22</v>
@@ -92826,13 +92642,13 @@
     </row>
     <row r="1639" spans="1:18">
       <c r="A1639" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1639" t="s">
         <v>22</v>
       </c>
       <c r="C1639" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1639" t="s">
         <v>22</v>
@@ -92882,13 +92698,13 @@
     </row>
     <row r="1640" spans="1:18">
       <c r="A1640" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1640" t="s">
         <v>22</v>
       </c>
       <c r="C1640" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1640" t="s">
         <v>22</v>
@@ -92900,7 +92716,7 @@
         <v>22</v>
       </c>
       <c r="G1640" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1640" t="s">
         <v>22</v>
@@ -92938,13 +92754,13 @@
     </row>
     <row r="1641" spans="1:18">
       <c r="A1641" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1641" t="s">
         <v>22</v>
       </c>
       <c r="C1641" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1641" t="s">
         <v>22</v>
@@ -92994,13 +92810,13 @@
     </row>
     <row r="1642" spans="1:18">
       <c r="A1642" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1642" t="s">
         <v>22</v>
       </c>
       <c r="C1642" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1642" t="s">
         <v>22</v>
@@ -93050,13 +92866,13 @@
     </row>
     <row r="1643" spans="1:18">
       <c r="A1643" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1643" t="s">
         <v>22</v>
       </c>
       <c r="C1643" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1643" t="s">
         <v>22</v>
@@ -93106,13 +92922,13 @@
     </row>
     <row r="1644" spans="1:18">
       <c r="A1644" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1644" t="s">
         <v>22</v>
       </c>
       <c r="C1644" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1644" t="s">
         <v>22</v>
@@ -93162,13 +92978,13 @@
     </row>
     <row r="1645" spans="1:18">
       <c r="A1645" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1645" t="s">
         <v>22</v>
       </c>
       <c r="C1645" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1645" t="s">
         <v>22</v>
@@ -93218,13 +93034,13 @@
     </row>
     <row r="1646" spans="1:18">
       <c r="A1646" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1646" t="s">
         <v>22</v>
       </c>
       <c r="C1646" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1646" t="s">
         <v>22</v>
@@ -93274,13 +93090,13 @@
     </row>
     <row r="1647" spans="1:18">
       <c r="A1647" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B1647" t="s">
         <v>22</v>
       </c>
       <c r="C1647" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D1647" t="s">
         <v>22</v>
@@ -93330,13 +93146,13 @@
     </row>
     <row r="1648" spans="1:18">
       <c r="A1648" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1648" t="s">
         <v>22</v>
       </c>
       <c r="C1648" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1648" t="s">
         <v>22</v>
@@ -93386,13 +93202,13 @@
     </row>
     <row r="1649" spans="1:18">
       <c r="A1649" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1649" t="s">
         <v>22</v>
       </c>
       <c r="C1649" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1649" t="s">
         <v>22</v>
@@ -93442,13 +93258,13 @@
     </row>
     <row r="1650" spans="1:18">
       <c r="A1650" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1650" t="s">
         <v>22</v>
       </c>
       <c r="C1650" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1650" t="s">
         <v>22</v>
@@ -93498,13 +93314,13 @@
     </row>
     <row r="1651" spans="1:18">
       <c r="A1651" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1651" t="s">
         <v>22</v>
       </c>
       <c r="C1651" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1651" t="s">
         <v>22</v>
@@ -93554,13 +93370,13 @@
     </row>
     <row r="1652" spans="1:18">
       <c r="A1652" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1652" t="s">
         <v>22</v>
       </c>
       <c r="C1652" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1652" t="s">
         <v>22</v>
@@ -93610,13 +93426,13 @@
     </row>
     <row r="1653" spans="1:18">
       <c r="A1653" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1653" t="s">
         <v>22</v>
       </c>
       <c r="C1653" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1653" t="s">
         <v>22</v>
@@ -93666,19 +93482,19 @@
     </row>
     <row r="1654" spans="1:18">
       <c r="A1654" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1654" t="s">
         <v>22</v>
       </c>
       <c r="C1654" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1654" t="s">
         <v>22</v>
       </c>
       <c r="E1654" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="F1654" t="s">
         <v>22</v>
@@ -93722,13 +93538,13 @@
     </row>
     <row r="1655" spans="1:18">
       <c r="A1655" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1655" t="s">
         <v>22</v>
       </c>
       <c r="C1655" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1655" t="s">
         <v>22</v>
@@ -93778,13 +93594,13 @@
     </row>
     <row r="1656" spans="1:18">
       <c r="A1656" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1656" t="s">
         <v>22</v>
       </c>
       <c r="C1656" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1656" t="s">
         <v>22</v>
@@ -93834,13 +93650,13 @@
     </row>
     <row r="1657" spans="1:18">
       <c r="A1657" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1657" t="s">
         <v>22</v>
       </c>
       <c r="C1657" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1657" t="s">
         <v>22</v>
@@ -93890,13 +93706,13 @@
     </row>
     <row r="1658" spans="1:18">
       <c r="A1658" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1658" t="s">
         <v>22</v>
       </c>
       <c r="C1658" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1658" t="s">
         <v>22</v>
@@ -93946,13 +93762,13 @@
     </row>
     <row r="1659" spans="1:18">
       <c r="A1659" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1659" t="s">
         <v>22</v>
       </c>
       <c r="C1659" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1659" t="s">
         <v>22</v>
@@ -94002,13 +93818,13 @@
     </row>
     <row r="1660" spans="1:18">
       <c r="A1660" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1660" t="s">
         <v>22</v>
       </c>
       <c r="C1660" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1660" t="s">
         <v>22</v>
@@ -94058,19 +93874,19 @@
     </row>
     <row r="1661" spans="1:18">
       <c r="A1661" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1661" t="s">
         <v>22</v>
       </c>
       <c r="C1661" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1661" t="s">
         <v>22</v>
       </c>
       <c r="E1661" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="F1661" t="s">
         <v>22</v>
@@ -94114,13 +93930,13 @@
     </row>
     <row r="1662" spans="1:18">
       <c r="A1662" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1662" t="s">
         <v>22</v>
       </c>
       <c r="C1662" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1662" t="s">
         <v>22</v>
@@ -94170,13 +93986,13 @@
     </row>
     <row r="1663" spans="1:18">
       <c r="A1663" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1663" t="s">
         <v>22</v>
       </c>
       <c r="C1663" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1663" t="s">
         <v>22</v>
@@ -94226,13 +94042,13 @@
     </row>
     <row r="1664" spans="1:18">
       <c r="A1664" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1664" t="s">
         <v>22</v>
       </c>
       <c r="C1664" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1664" t="s">
         <v>22</v>
@@ -94282,13 +94098,13 @@
     </row>
     <row r="1665" spans="1:18">
       <c r="A1665" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1665" t="s">
         <v>22</v>
       </c>
       <c r="C1665" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1665" t="s">
         <v>22</v>
@@ -94338,13 +94154,13 @@
     </row>
     <row r="1666" spans="1:18">
       <c r="A1666" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1666" t="s">
         <v>22</v>
       </c>
       <c r="C1666" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1666" t="s">
         <v>22</v>
@@ -94394,13 +94210,13 @@
     </row>
     <row r="1667" spans="1:18">
       <c r="A1667" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1667" t="s">
         <v>22</v>
       </c>
       <c r="C1667" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1667" t="s">
         <v>22</v>
@@ -94450,13 +94266,13 @@
     </row>
     <row r="1668" spans="1:18">
       <c r="A1668" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1668" t="s">
         <v>22</v>
       </c>
       <c r="C1668" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1668" t="s">
         <v>22</v>
@@ -94506,13 +94322,13 @@
     </row>
     <row r="1669" spans="1:18">
       <c r="A1669" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1669" t="s">
         <v>22</v>
       </c>
       <c r="C1669" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1669" t="s">
         <v>22</v>
@@ -94562,13 +94378,13 @@
     </row>
     <row r="1670" spans="1:18">
       <c r="A1670" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1670" t="s">
         <v>22</v>
       </c>
       <c r="C1670" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1670" t="s">
         <v>22</v>
@@ -94618,13 +94434,13 @@
     </row>
     <row r="1671" spans="1:18">
       <c r="A1671" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1671" t="s">
         <v>22</v>
       </c>
       <c r="C1671" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1671" t="s">
         <v>22</v>
@@ -94674,13 +94490,13 @@
     </row>
     <row r="1672" spans="1:18">
       <c r="A1672" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1672" t="s">
         <v>22</v>
       </c>
       <c r="C1672" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1672" t="s">
         <v>22</v>
@@ -94730,13 +94546,13 @@
     </row>
     <row r="1673" spans="1:18">
       <c r="A1673" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1673" t="s">
         <v>22</v>
       </c>
       <c r="C1673" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1673" t="s">
         <v>22</v>
@@ -94786,13 +94602,13 @@
     </row>
     <row r="1674" spans="1:18">
       <c r="A1674" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1674" t="s">
         <v>22</v>
       </c>
       <c r="C1674" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1674" t="s">
         <v>22</v>
@@ -94842,13 +94658,13 @@
     </row>
     <row r="1675" spans="1:18">
       <c r="A1675" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1675" t="s">
         <v>22</v>
       </c>
       <c r="C1675" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1675" t="s">
         <v>22</v>
@@ -94898,13 +94714,13 @@
     </row>
     <row r="1676" spans="1:18">
       <c r="A1676" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1676" t="s">
         <v>22</v>
       </c>
       <c r="C1676" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1676" t="s">
         <v>22</v>
@@ -94954,13 +94770,13 @@
     </row>
     <row r="1677" spans="1:18">
       <c r="A1677" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1677" t="s">
         <v>22</v>
       </c>
       <c r="C1677" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1677" t="s">
         <v>22</v>
@@ -95010,13 +94826,13 @@
     </row>
     <row r="1678" spans="1:18">
       <c r="A1678" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1678" t="s">
         <v>22</v>
       </c>
       <c r="C1678" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1678" t="s">
         <v>22</v>
@@ -95066,13 +94882,13 @@
     </row>
     <row r="1679" spans="1:18">
       <c r="A1679" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1679" t="s">
         <v>22</v>
       </c>
       <c r="C1679" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1679" t="s">
         <v>22</v>
@@ -95122,13 +94938,13 @@
     </row>
     <row r="1680" spans="1:18">
       <c r="A1680" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1680" t="s">
         <v>22</v>
       </c>
       <c r="C1680" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1680" t="s">
         <v>22</v>
@@ -95178,13 +94994,13 @@
     </row>
     <row r="1681" spans="1:18">
       <c r="A1681" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1681" t="s">
         <v>22</v>
       </c>
       <c r="C1681" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1681" t="s">
         <v>22</v>
@@ -95234,13 +95050,13 @@
     </row>
     <row r="1682" spans="1:18">
       <c r="A1682" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1682" t="s">
         <v>22</v>
       </c>
       <c r="C1682" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1682" t="s">
         <v>22</v>
@@ -95290,13 +95106,13 @@
     </row>
     <row r="1683" spans="1:18">
       <c r="A1683" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1683" t="s">
         <v>22</v>
       </c>
       <c r="C1683" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1683" t="s">
         <v>22</v>
@@ -95346,13 +95162,13 @@
     </row>
     <row r="1684" spans="1:18">
       <c r="A1684" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1684" t="s">
         <v>22</v>
       </c>
       <c r="C1684" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1684" t="s">
         <v>22</v>
@@ -95402,13 +95218,13 @@
     </row>
     <row r="1685" spans="1:18">
       <c r="A1685" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B1685" t="s">
         <v>22</v>
       </c>
       <c r="C1685" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D1685" t="s">
         <v>22</v>
@@ -95458,19 +95274,19 @@
     </row>
     <row r="1686" spans="1:18">
       <c r="A1686" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B1686" t="s">
         <v>22</v>
       </c>
       <c r="C1686" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D1686" t="s">
         <v>22</v>
       </c>
       <c r="E1686" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="F1686" t="s">
         <v>22</v>
@@ -95514,13 +95330,13 @@
     </row>
     <row r="1687" spans="1:18">
       <c r="A1687" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B1687" t="s">
         <v>22</v>
       </c>
       <c r="C1687" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D1687" t="s">
         <v>22</v>
@@ -95570,13 +95386,13 @@
     </row>
     <row r="1688" spans="1:18">
       <c r="A1688" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B1688" t="s">
         <v>22</v>
       </c>
       <c r="C1688" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D1688" t="s">
         <v>22</v>
@@ -95626,13 +95442,13 @@
     </row>
     <row r="1689" spans="1:18">
       <c r="A1689" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B1689" t="s">
         <v>22</v>
       </c>
       <c r="C1689" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D1689" t="s">
         <v>22</v>
@@ -95644,7 +95460,7 @@
         <v>22</v>
       </c>
       <c r="G1689" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="H1689" t="s">
         <v>22</v>
@@ -95682,13 +95498,13 @@
     </row>
     <row r="1690" spans="1:18">
       <c r="A1690" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B1690" t="s">
         <v>22</v>
       </c>
       <c r="C1690" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D1690" t="s">
         <v>22</v>
@@ -95738,19 +95554,19 @@
     </row>
     <row r="1691" spans="1:18">
       <c r="A1691" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B1691" t="s">
         <v>22</v>
       </c>
       <c r="C1691" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D1691" t="s">
         <v>22</v>
       </c>
       <c r="E1691" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="F1691" t="s">
         <v>22</v>
@@ -95794,13 +95610,13 @@
     </row>
     <row r="1692" spans="1:18">
       <c r="A1692" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B1692" t="s">
         <v>22</v>
       </c>
       <c r="C1692" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D1692" t="s">
         <v>22</v>
@@ -95850,13 +95666,13 @@
     </row>
     <row r="1693" spans="1:18">
       <c r="A1693" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B1693" t="s">
         <v>22</v>
       </c>
       <c r="C1693" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D1693" t="s">
         <v>22</v>
@@ -95868,7 +95684,7 @@
         <v>22</v>
       </c>
       <c r="G1693" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="H1693" t="s">
         <v>22</v>
@@ -95906,13 +95722,13 @@
     </row>
     <row r="1694" spans="1:18">
       <c r="A1694" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B1694" t="s">
         <v>22</v>
       </c>
       <c r="C1694" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D1694" t="s">
         <v>22</v>
@@ -95954,7 +95770,7 @@
         <v>22</v>
       </c>
       <c r="Q1694" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="R1694" t="s">
         <v>22</v>
@@ -95962,13 +95778,13 @@
     </row>
     <row r="1695" spans="1:18">
       <c r="A1695" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1695" t="s">
         <v>22</v>
       </c>
       <c r="C1695" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1695" t="s">
         <v>22</v>
@@ -96018,13 +95834,13 @@
     </row>
     <row r="1696" spans="1:18">
       <c r="A1696" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1696" t="s">
         <v>22</v>
       </c>
       <c r="C1696" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1696" t="s">
         <v>22</v>
@@ -96074,19 +95890,19 @@
     </row>
     <row r="1697" spans="1:18">
       <c r="A1697" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1697" t="s">
         <v>22</v>
       </c>
       <c r="C1697" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1697" t="s">
         <v>22</v>
       </c>
       <c r="E1697" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="F1697" t="s">
         <v>22</v>
@@ -96130,19 +95946,19 @@
     </row>
     <row r="1698" spans="1:18">
       <c r="A1698" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1698" t="s">
         <v>22</v>
       </c>
       <c r="C1698" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1698" t="s">
         <v>22</v>
       </c>
       <c r="E1698" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="F1698" t="s">
         <v>22</v>
@@ -96186,13 +96002,13 @@
     </row>
     <row r="1699" spans="1:18">
       <c r="A1699" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1699" t="s">
         <v>22</v>
       </c>
       <c r="C1699" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1699" t="s">
         <v>22</v>
@@ -96242,13 +96058,13 @@
     </row>
     <row r="1700" spans="1:18">
       <c r="A1700" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1700" t="s">
         <v>22</v>
       </c>
       <c r="C1700" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1700" t="s">
         <v>22</v>
@@ -96298,13 +96114,13 @@
     </row>
     <row r="1701" spans="1:18">
       <c r="A1701" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1701" t="s">
         <v>22</v>
       </c>
       <c r="C1701" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1701" t="s">
         <v>22</v>
@@ -96354,13 +96170,13 @@
     </row>
     <row r="1702" spans="1:18">
       <c r="A1702" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1702" t="s">
         <v>22</v>
       </c>
       <c r="C1702" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1702" t="s">
         <v>22</v>
@@ -96410,13 +96226,13 @@
     </row>
     <row r="1703" spans="1:18">
       <c r="A1703" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1703" t="s">
         <v>22</v>
       </c>
       <c r="C1703" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1703" t="s">
         <v>22</v>
@@ -96466,13 +96282,13 @@
     </row>
     <row r="1704" spans="1:18">
       <c r="A1704" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1704" t="s">
         <v>22</v>
       </c>
       <c r="C1704" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1704" t="s">
         <v>22</v>
@@ -96522,13 +96338,13 @@
     </row>
     <row r="1705" spans="1:18">
       <c r="A1705" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1705" t="s">
         <v>22</v>
       </c>
       <c r="C1705" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1705" t="s">
         <v>22</v>
@@ -96578,13 +96394,13 @@
     </row>
     <row r="1706" spans="1:18">
       <c r="A1706" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1706" t="s">
         <v>22</v>
       </c>
       <c r="C1706" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1706" t="s">
         <v>22</v>
@@ -96634,13 +96450,13 @@
     </row>
     <row r="1707" spans="1:18">
       <c r="A1707" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1707" t="s">
         <v>22</v>
       </c>
       <c r="C1707" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1707" t="s">
         <v>22</v>
@@ -96690,13 +96506,13 @@
     </row>
     <row r="1708" spans="1:18">
       <c r="A1708" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1708" t="s">
         <v>22</v>
       </c>
       <c r="C1708" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1708" t="s">
         <v>22</v>
@@ -96746,13 +96562,13 @@
     </row>
     <row r="1709" spans="1:18">
       <c r="A1709" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1709" t="s">
         <v>22</v>
       </c>
       <c r="C1709" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1709" t="s">
         <v>22</v>
@@ -96802,13 +96618,13 @@
     </row>
     <row r="1710" spans="1:18">
       <c r="A1710" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1710" t="s">
         <v>22</v>
       </c>
       <c r="C1710" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1710" t="s">
         <v>22</v>
@@ -96858,13 +96674,13 @@
     </row>
     <row r="1711" spans="1:18">
       <c r="A1711" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1711" t="s">
         <v>22</v>
       </c>
       <c r="C1711" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1711" t="s">
         <v>22</v>
@@ -96914,13 +96730,13 @@
     </row>
     <row r="1712" spans="1:18">
       <c r="A1712" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1712" t="s">
         <v>22</v>
       </c>
       <c r="C1712" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1712" t="s">
         <v>22</v>
@@ -96970,13 +96786,13 @@
     </row>
     <row r="1713" spans="1:18">
       <c r="A1713" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1713" t="s">
         <v>22</v>
       </c>
       <c r="C1713" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1713" t="s">
         <v>22</v>
@@ -97026,13 +96842,13 @@
     </row>
     <row r="1714" spans="1:18">
       <c r="A1714" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1714" t="s">
         <v>22</v>
       </c>
       <c r="C1714" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1714" t="s">
         <v>22</v>
@@ -97082,13 +96898,13 @@
     </row>
     <row r="1715" spans="1:18">
       <c r="A1715" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1715" t="s">
         <v>22</v>
       </c>
       <c r="C1715" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1715" t="s">
         <v>22</v>
@@ -97138,13 +96954,13 @@
     </row>
     <row r="1716" spans="1:18">
       <c r="A1716" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1716" t="s">
         <v>22</v>
       </c>
       <c r="C1716" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1716" t="s">
         <v>22</v>
@@ -97168,7 +96984,7 @@
         <v>22</v>
       </c>
       <c r="K1716" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="L1716" t="s">
         <v>22</v>
@@ -97194,13 +97010,13 @@
     </row>
     <row r="1717" spans="1:18">
       <c r="A1717" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1717" t="s">
         <v>22</v>
       </c>
       <c r="C1717" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1717" t="s">
         <v>22</v>
@@ -97224,7 +97040,7 @@
         <v>22</v>
       </c>
       <c r="K1717" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="L1717" t="s">
         <v>22</v>
@@ -97250,13 +97066,13 @@
     </row>
     <row r="1718" spans="1:18">
       <c r="A1718" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1718" t="s">
         <v>22</v>
       </c>
       <c r="C1718" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1718" t="s">
         <v>22</v>
@@ -97306,13 +97122,13 @@
     </row>
     <row r="1719" spans="1:18">
       <c r="A1719" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B1719" t="s">
         <v>22</v>
       </c>
       <c r="C1719" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D1719" t="s">
         <v>22</v>
@@ -97354,7 +97170,7 @@
         <v>22</v>
       </c>
       <c r="Q1719" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="R1719" t="s">
         <v>22</v>
@@ -97362,13 +97178,13 @@
     </row>
     <row r="1720" spans="1:18">
       <c r="A1720" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1720" t="s">
         <v>22</v>
       </c>
       <c r="C1720" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1720" t="s">
         <v>22</v>
@@ -97418,13 +97234,13 @@
     </row>
     <row r="1721" spans="1:18">
       <c r="A1721" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1721" t="s">
         <v>22</v>
       </c>
       <c r="C1721" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1721" t="s">
         <v>22</v>
@@ -97474,13 +97290,13 @@
     </row>
     <row r="1722" spans="1:18">
       <c r="A1722" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1722" t="s">
         <v>22</v>
       </c>
       <c r="C1722" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1722" t="s">
         <v>22</v>
@@ -97530,19 +97346,19 @@
     </row>
     <row r="1723" spans="1:18">
       <c r="A1723" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1723" t="s">
         <v>22</v>
       </c>
       <c r="C1723" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1723" t="s">
         <v>22</v>
       </c>
       <c r="E1723" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="F1723" t="s">
         <v>22</v>
@@ -97586,19 +97402,19 @@
     </row>
     <row r="1724" spans="1:18">
       <c r="A1724" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1724" t="s">
         <v>22</v>
       </c>
       <c r="C1724" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1724" t="s">
         <v>22</v>
       </c>
       <c r="E1724" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="F1724" t="s">
         <v>22</v>
@@ -97642,13 +97458,13 @@
     </row>
     <row r="1725" spans="1:18">
       <c r="A1725" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1725" t="s">
         <v>22</v>
       </c>
       <c r="C1725" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1725" t="s">
         <v>22</v>
@@ -97698,13 +97514,13 @@
     </row>
     <row r="1726" spans="1:18">
       <c r="A1726" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1726" t="s">
         <v>22</v>
       </c>
       <c r="C1726" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1726" t="s">
         <v>22</v>
@@ -97716,7 +97532,7 @@
         <v>22</v>
       </c>
       <c r="G1726" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="H1726" t="s">
         <v>22</v>
@@ -97754,13 +97570,13 @@
     </row>
     <row r="1727" spans="1:18">
       <c r="A1727" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1727" t="s">
         <v>22</v>
       </c>
       <c r="C1727" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1727" t="s">
         <v>22</v>
@@ -97810,13 +97626,13 @@
     </row>
     <row r="1728" spans="1:18">
       <c r="A1728" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1728" t="s">
         <v>22</v>
       </c>
       <c r="C1728" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1728" t="s">
         <v>22</v>
@@ -97866,13 +97682,13 @@
     </row>
     <row r="1729" spans="1:18">
       <c r="A1729" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1729" t="s">
         <v>22</v>
       </c>
       <c r="C1729" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1729" t="s">
         <v>22</v>
@@ -97922,13 +97738,13 @@
     </row>
     <row r="1730" spans="1:18">
       <c r="A1730" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1730" t="s">
         <v>22</v>
       </c>
       <c r="C1730" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1730" t="s">
         <v>22</v>
@@ -97978,13 +97794,13 @@
     </row>
     <row r="1731" spans="1:18">
       <c r="A1731" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1731" t="s">
         <v>22</v>
       </c>
       <c r="C1731" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1731" t="s">
         <v>22</v>
@@ -98034,13 +97850,13 @@
     </row>
     <row r="1732" spans="1:18">
       <c r="A1732" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1732" t="s">
         <v>22</v>
       </c>
       <c r="C1732" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1732" t="s">
         <v>22</v>
@@ -98090,13 +97906,13 @@
     </row>
     <row r="1733" spans="1:18">
       <c r="A1733" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1733" t="s">
         <v>22</v>
       </c>
       <c r="C1733" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1733" t="s">
         <v>22</v>
@@ -98146,13 +97962,13 @@
     </row>
     <row r="1734" spans="1:18">
       <c r="A1734" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1734" t="s">
         <v>22</v>
       </c>
       <c r="C1734" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1734" t="s">
         <v>22</v>
@@ -98194,7 +98010,7 @@
         <v>22</v>
       </c>
       <c r="Q1734" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="R1734" t="s">
         <v>22</v>
@@ -98202,13 +98018,13 @@
     </row>
     <row r="1735" spans="1:18">
       <c r="A1735" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1735" t="s">
         <v>22</v>
       </c>
       <c r="C1735" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1735" t="s">
         <v>22</v>
@@ -98250,7 +98066,7 @@
         <v>22</v>
       </c>
       <c r="Q1735" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="R1735" t="s">
         <v>22</v>
@@ -98258,13 +98074,13 @@
     </row>
     <row r="1736" spans="1:18">
       <c r="A1736" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1736" t="s">
         <v>22</v>
       </c>
       <c r="C1736" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1736" t="s">
         <v>22</v>
@@ -98306,7 +98122,7 @@
         <v>22</v>
       </c>
       <c r="Q1736" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="R1736" t="s">
         <v>22</v>
@@ -98314,13 +98130,13 @@
     </row>
     <row r="1737" spans="1:18">
       <c r="A1737" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1737" t="s">
         <v>22</v>
       </c>
       <c r="C1737" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1737" t="s">
         <v>22</v>
@@ -98362,7 +98178,7 @@
         <v>22</v>
       </c>
       <c r="Q1737" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="R1737" t="s">
         <v>22</v>
@@ -98370,13 +98186,13 @@
     </row>
     <row r="1738" spans="1:18">
       <c r="A1738" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B1738" t="s">
         <v>22</v>
       </c>
       <c r="C1738" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D1738" t="s">
         <v>22</v>
@@ -98426,16 +98242,16 @@
     </row>
     <row r="1739" spans="1:18">
       <c r="A1739" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1739" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1739" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1739" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1739" t="s">
         <v>133</v>
@@ -98482,16 +98298,16 @@
     </row>
     <row r="1740" spans="1:18">
       <c r="A1740" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1740" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1740" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1740" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1740" t="s">
         <v>258</v>
@@ -98538,16 +98354,16 @@
     </row>
     <row r="1741" spans="1:18">
       <c r="A1741" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1741" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1741" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1741" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1741" t="s">
         <v>430</v>
@@ -98594,19 +98410,19 @@
     </row>
     <row r="1742" spans="1:18">
       <c r="A1742" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1742" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1742" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1742" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1742" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="F1742" t="s">
         <v>484</v>
@@ -98650,19 +98466,19 @@
     </row>
     <row r="1743" spans="1:18">
       <c r="A1743" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1743" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1743" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1743" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1743" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="F1743" t="s">
         <v>484</v>
@@ -98706,16 +98522,16 @@
     </row>
     <row r="1744" spans="1:18">
       <c r="A1744" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1744" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1744" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1744" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1744" t="s">
         <v>206</v>
@@ -98762,16 +98578,16 @@
     </row>
     <row r="1745" spans="1:18">
       <c r="A1745" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1745" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1745" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1745" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1745" t="s">
         <v>22</v>
@@ -98780,7 +98596,7 @@
         <v>484</v>
       </c>
       <c r="G1745" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="H1745" t="s">
         <v>22</v>
@@ -98818,16 +98634,16 @@
     </row>
     <row r="1746" spans="1:18">
       <c r="A1746" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1746" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1746" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1746" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1746" t="s">
         <v>22</v>
@@ -98874,16 +98690,16 @@
     </row>
     <row r="1747" spans="1:18">
       <c r="A1747" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1747" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1747" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1747" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1747" t="s">
         <v>22</v>
@@ -98930,16 +98746,16 @@
     </row>
     <row r="1748" spans="1:18">
       <c r="A1748" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1748" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1748" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1748" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1748" t="s">
         <v>22</v>
@@ -98986,16 +98802,16 @@
     </row>
     <row r="1749" spans="1:18">
       <c r="A1749" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1749" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1749" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1749" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1749" t="s">
         <v>22</v>
@@ -99042,16 +98858,16 @@
     </row>
     <row r="1750" spans="1:18">
       <c r="A1750" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1750" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1750" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1750" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1750" t="s">
         <v>22</v>
@@ -99098,16 +98914,16 @@
     </row>
     <row r="1751" spans="1:18">
       <c r="A1751" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1751" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1751" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1751" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1751" t="s">
         <v>22</v>
@@ -99154,16 +98970,16 @@
     </row>
     <row r="1752" spans="1:18">
       <c r="A1752" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1752" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1752" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1752" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1752" t="s">
         <v>22</v>
@@ -99210,16 +99026,16 @@
     </row>
     <row r="1753" spans="1:18">
       <c r="A1753" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1753" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1753" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1753" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1753" t="s">
         <v>22</v>
@@ -99258,7 +99074,7 @@
         <v>22</v>
       </c>
       <c r="Q1753" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="R1753" t="s">
         <v>22</v>
@@ -99266,16 +99082,16 @@
     </row>
     <row r="1754" spans="1:18">
       <c r="A1754" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B1754" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C1754" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D1754" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="E1754" t="s">
         <v>22</v>
@@ -99314,7 +99130,7 @@
         <v>22</v>
       </c>
       <c r="Q1754" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="R1754" t="s">
         <v>22</v>
@@ -99322,13 +99138,13 @@
     </row>
     <row r="1755" spans="1:18">
       <c r="A1755" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B1755" t="s">
         <v>22</v>
       </c>
       <c r="C1755" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D1755" t="s">
         <v>22</v>
@@ -99378,13 +99194,13 @@
     </row>
     <row r="1756" spans="1:18">
       <c r="A1756" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B1756" t="s">
         <v>22</v>
       </c>
       <c r="C1756" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D1756" t="s">
         <v>22</v>
@@ -99434,19 +99250,19 @@
     </row>
     <row r="1757" spans="1:18">
       <c r="A1757" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B1757" t="s">
         <v>22</v>
       </c>
       <c r="C1757" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D1757" t="s">
         <v>22</v>
       </c>
       <c r="E1757" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="F1757" t="s">
         <v>22</v>
@@ -99490,19 +99306,19 @@
     </row>
     <row r="1758" spans="1:18">
       <c r="A1758" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B1758" t="s">
         <v>22</v>
       </c>
       <c r="C1758" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D1758" t="s">
         <v>22</v>
       </c>
       <c r="E1758" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="F1758" t="s">
         <v>22</v>
@@ -99546,13 +99362,13 @@
     </row>
     <row r="1759" spans="1:18">
       <c r="A1759" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B1759" t="s">
         <v>22</v>
       </c>
       <c r="C1759" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D1759" t="s">
         <v>22</v>
@@ -99602,13 +99418,13 @@
     </row>
     <row r="1760" spans="1:18">
       <c r="A1760" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B1760" t="s">
         <v>22</v>
       </c>
       <c r="C1760" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D1760" t="s">
         <v>22</v>
@@ -99658,13 +99474,13 @@
     </row>
     <row r="1761" spans="1:18">
       <c r="A1761" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B1761" t="s">
         <v>22</v>
       </c>
       <c r="C1761" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D1761" t="s">
         <v>22</v>
@@ -99714,13 +99530,13 @@
     </row>
     <row r="1762" spans="1:18">
       <c r="A1762" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B1762" t="s">
         <v>22</v>
       </c>
       <c r="C1762" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D1762" t="s">
         <v>22</v>
@@ -99770,13 +99586,13 @@
     </row>
     <row r="1763" spans="1:18">
       <c r="A1763" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B1763" t="s">
         <v>22</v>
       </c>
       <c r="C1763" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D1763" t="s">
         <v>22</v>
@@ -99826,13 +99642,13 @@
     </row>
     <row r="1764" spans="1:18">
       <c r="A1764" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="B1764" t="s">
         <v>22</v>
       </c>
       <c r="C1764" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D1764" t="s">
         <v>22</v>
@@ -99882,19 +99698,19 @@
     </row>
     <row r="1765" spans="1:18">
       <c r="A1765" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="B1765" t="s">
         <v>22</v>
       </c>
       <c r="C1765" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="D1765" t="s">
         <v>22</v>
       </c>
       <c r="E1765" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="F1765" t="s">
         <v>22</v>
@@ -99938,13 +99754,13 @@
     </row>
     <row r="1766" spans="1:18">
       <c r="A1766" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B1766" t="s">
         <v>22</v>
       </c>
       <c r="C1766" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D1766" t="s">
         <v>22</v>
@@ -99994,13 +99810,13 @@
     </row>
     <row r="1767" spans="1:18">
       <c r="A1767" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B1767" t="s">
         <v>22</v>
       </c>
       <c r="C1767" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D1767" t="s">
         <v>22</v>
@@ -100050,13 +99866,13 @@
     </row>
     <row r="1768" spans="1:18">
       <c r="A1768" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B1768" t="s">
         <v>22</v>
       </c>
       <c r="C1768" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D1768" t="s">
         <v>22</v>
@@ -100106,13 +99922,13 @@
     </row>
     <row r="1769" spans="1:18">
       <c r="A1769" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B1769" t="s">
         <v>22</v>
       </c>
       <c r="C1769" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D1769" t="s">
         <v>22</v>
@@ -100162,13 +99978,13 @@
     </row>
     <row r="1770" spans="1:18">
       <c r="A1770" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B1770" t="s">
         <v>22</v>
       </c>
       <c r="C1770" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D1770" t="s">
         <v>22</v>
@@ -100186,7 +100002,7 @@
         <v>22</v>
       </c>
       <c r="I1770" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="J1770" t="s">
         <v>22</v>
@@ -100218,13 +100034,13 @@
     </row>
     <row r="1771" spans="1:18">
       <c r="A1771" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B1771" t="s">
         <v>22</v>
       </c>
       <c r="C1771" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D1771" t="s">
         <v>22</v>
@@ -100274,13 +100090,13 @@
     </row>
     <row r="1772" spans="1:18">
       <c r="A1772" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1772" t="s">
         <v>22</v>
       </c>
       <c r="C1772" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1772" t="s">
         <v>22</v>
@@ -100330,13 +100146,13 @@
     </row>
     <row r="1773" spans="1:18">
       <c r="A1773" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1773" t="s">
         <v>22</v>
       </c>
       <c r="C1773" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1773" t="s">
         <v>22</v>
@@ -100386,13 +100202,13 @@
     </row>
     <row r="1774" spans="1:18">
       <c r="A1774" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1774" t="s">
         <v>22</v>
       </c>
       <c r="C1774" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1774" t="s">
         <v>22</v>
@@ -100442,13 +100258,13 @@
     </row>
     <row r="1775" spans="1:18">
       <c r="A1775" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1775" t="s">
         <v>22</v>
       </c>
       <c r="C1775" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1775" t="s">
         <v>22</v>
@@ -100498,13 +100314,13 @@
     </row>
     <row r="1776" spans="1:18">
       <c r="A1776" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1776" t="s">
         <v>22</v>
       </c>
       <c r="C1776" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1776" t="s">
         <v>22</v>
@@ -100554,13 +100370,13 @@
     </row>
     <row r="1777" spans="1:18">
       <c r="A1777" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1777" t="s">
         <v>22</v>
       </c>
       <c r="C1777" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1777" t="s">
         <v>22</v>
@@ -100610,13 +100426,13 @@
     </row>
     <row r="1778" spans="1:18">
       <c r="A1778" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1778" t="s">
         <v>22</v>
       </c>
       <c r="C1778" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1778" t="s">
         <v>22</v>
@@ -100666,13 +100482,13 @@
     </row>
     <row r="1779" spans="1:18">
       <c r="A1779" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1779" t="s">
         <v>22</v>
       </c>
       <c r="C1779" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1779" t="s">
         <v>22</v>
@@ -100722,13 +100538,13 @@
     </row>
     <row r="1780" spans="1:18">
       <c r="A1780" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1780" t="s">
         <v>22</v>
       </c>
       <c r="C1780" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1780" t="s">
         <v>22</v>
@@ -100778,13 +100594,13 @@
     </row>
     <row r="1781" spans="1:18">
       <c r="A1781" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1781" t="s">
         <v>22</v>
       </c>
       <c r="C1781" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1781" t="s">
         <v>22</v>
@@ -100834,13 +100650,13 @@
     </row>
     <row r="1782" spans="1:18">
       <c r="A1782" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1782" t="s">
         <v>22</v>
       </c>
       <c r="C1782" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1782" t="s">
         <v>22</v>
@@ -100890,13 +100706,13 @@
     </row>
     <row r="1783" spans="1:18">
       <c r="A1783" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1783" t="s">
         <v>22</v>
       </c>
       <c r="C1783" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1783" t="s">
         <v>22</v>
@@ -100946,13 +100762,13 @@
     </row>
     <row r="1784" spans="1:18">
       <c r="A1784" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1784" t="s">
         <v>22</v>
       </c>
       <c r="C1784" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1784" t="s">
         <v>22</v>
@@ -101002,13 +100818,13 @@
     </row>
     <row r="1785" spans="1:18">
       <c r="A1785" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1785" t="s">
         <v>22</v>
       </c>
       <c r="C1785" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1785" t="s">
         <v>22</v>
@@ -101058,13 +100874,13 @@
     </row>
     <row r="1786" spans="1:18">
       <c r="A1786" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1786" t="s">
         <v>22</v>
       </c>
       <c r="C1786" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1786" t="s">
         <v>22</v>
@@ -101114,13 +100930,13 @@
     </row>
     <row r="1787" spans="1:18">
       <c r="A1787" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1787" t="s">
         <v>22</v>
       </c>
       <c r="C1787" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1787" t="s">
         <v>22</v>
@@ -101170,13 +100986,13 @@
     </row>
     <row r="1788" spans="1:18">
       <c r="A1788" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1788" t="s">
         <v>22</v>
       </c>
       <c r="C1788" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1788" t="s">
         <v>22</v>
@@ -101226,13 +101042,13 @@
     </row>
     <row r="1789" spans="1:18">
       <c r="A1789" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1789" t="s">
         <v>22</v>
       </c>
       <c r="C1789" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1789" t="s">
         <v>22</v>
@@ -101282,13 +101098,13 @@
     </row>
     <row r="1790" spans="1:18">
       <c r="A1790" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1790" t="s">
         <v>22</v>
       </c>
       <c r="C1790" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1790" t="s">
         <v>22</v>
@@ -101338,13 +101154,13 @@
     </row>
     <row r="1791" spans="1:18">
       <c r="A1791" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1791" t="s">
         <v>22</v>
       </c>
       <c r="C1791" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1791" t="s">
         <v>22</v>
@@ -101394,13 +101210,13 @@
     </row>
     <row r="1792" spans="1:18">
       <c r="A1792" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1792" t="s">
         <v>22</v>
       </c>
       <c r="C1792" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1792" t="s">
         <v>22</v>
@@ -101450,13 +101266,13 @@
     </row>
     <row r="1793" spans="1:18">
       <c r="A1793" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1793" t="s">
         <v>22</v>
       </c>
       <c r="C1793" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1793" t="s">
         <v>22</v>
@@ -101506,13 +101322,13 @@
     </row>
     <row r="1794" spans="1:18">
       <c r="A1794" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1794" t="s">
         <v>22</v>
       </c>
       <c r="C1794" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1794" t="s">
         <v>22</v>
@@ -101562,13 +101378,13 @@
     </row>
     <row r="1795" spans="1:18">
       <c r="A1795" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1795" t="s">
         <v>22</v>
       </c>
       <c r="C1795" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1795" t="s">
         <v>22</v>
@@ -101618,13 +101434,13 @@
     </row>
     <row r="1796" spans="1:18">
       <c r="A1796" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1796" t="s">
         <v>22</v>
       </c>
       <c r="C1796" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1796" t="s">
         <v>22</v>
@@ -101674,13 +101490,13 @@
     </row>
     <row r="1797" spans="1:18">
       <c r="A1797" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B1797" t="s">
         <v>22</v>
       </c>
       <c r="C1797" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1797" t="s">
         <v>22</v>
@@ -101730,13 +101546,13 @@
     </row>
     <row r="1798" spans="1:18">
       <c r="A1798" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1798" t="s">
         <v>22</v>
       </c>
       <c r="C1798" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1798" t="s">
         <v>22</v>
@@ -101786,13 +101602,13 @@
     </row>
     <row r="1799" spans="1:18">
       <c r="A1799" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1799" t="s">
         <v>22</v>
       </c>
       <c r="C1799" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1799" t="s">
         <v>22</v>
@@ -101842,13 +101658,13 @@
     </row>
     <row r="1800" spans="1:18">
       <c r="A1800" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1800" t="s">
         <v>22</v>
       </c>
       <c r="C1800" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1800" t="s">
         <v>22</v>
@@ -101898,13 +101714,13 @@
     </row>
     <row r="1801" spans="1:18">
       <c r="A1801" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1801" t="s">
         <v>22</v>
       </c>
       <c r="C1801" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1801" t="s">
         <v>22</v>
@@ -101954,13 +101770,13 @@
     </row>
     <row r="1802" spans="1:18">
       <c r="A1802" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1802" t="s">
         <v>22</v>
       </c>
       <c r="C1802" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1802" t="s">
         <v>22</v>
@@ -102010,13 +101826,13 @@
     </row>
     <row r="1803" spans="1:18">
       <c r="A1803" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1803" t="s">
         <v>22</v>
       </c>
       <c r="C1803" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1803" t="s">
         <v>22</v>
@@ -102066,13 +101882,13 @@
     </row>
     <row r="1804" spans="1:18">
       <c r="A1804" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1804" t="s">
         <v>22</v>
       </c>
       <c r="C1804" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1804" t="s">
         <v>22</v>
@@ -102122,13 +101938,13 @@
     </row>
     <row r="1805" spans="1:18">
       <c r="A1805" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1805" t="s">
         <v>22</v>
       </c>
       <c r="C1805" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1805" t="s">
         <v>22</v>
@@ -102178,13 +101994,13 @@
     </row>
     <row r="1806" spans="1:18">
       <c r="A1806" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1806" t="s">
         <v>22</v>
       </c>
       <c r="C1806" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1806" t="s">
         <v>22</v>
@@ -102234,13 +102050,13 @@
     </row>
     <row r="1807" spans="1:18">
       <c r="A1807" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1807" t="s">
         <v>22</v>
       </c>
       <c r="C1807" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1807" t="s">
         <v>22</v>
@@ -102290,13 +102106,13 @@
     </row>
     <row r="1808" spans="1:18">
       <c r="A1808" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1808" t="s">
         <v>22</v>
       </c>
       <c r="C1808" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1808" t="s">
         <v>22</v>
@@ -102346,13 +102162,13 @@
     </row>
     <row r="1809" spans="1:18">
       <c r="A1809" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1809" t="s">
         <v>22</v>
       </c>
       <c r="C1809" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1809" t="s">
         <v>22</v>
@@ -102402,13 +102218,13 @@
     </row>
     <row r="1810" spans="1:18">
       <c r="A1810" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1810" t="s">
         <v>22</v>
       </c>
       <c r="C1810" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1810" t="s">
         <v>22</v>
@@ -102458,13 +102274,13 @@
     </row>
     <row r="1811" spans="1:18">
       <c r="A1811" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1811" t="s">
         <v>22</v>
       </c>
       <c r="C1811" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1811" t="s">
         <v>22</v>
@@ -102514,13 +102330,13 @@
     </row>
     <row r="1812" spans="1:18">
       <c r="A1812" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1812" t="s">
         <v>22</v>
       </c>
       <c r="C1812" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1812" t="s">
         <v>22</v>
@@ -102570,13 +102386,13 @@
     </row>
     <row r="1813" spans="1:18">
       <c r="A1813" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1813" t="s">
         <v>22</v>
       </c>
       <c r="C1813" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1813" t="s">
         <v>22</v>
@@ -102626,13 +102442,13 @@
     </row>
     <row r="1814" spans="1:18">
       <c r="A1814" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1814" t="s">
         <v>22</v>
       </c>
       <c r="C1814" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1814" t="s">
         <v>22</v>
@@ -102682,13 +102498,13 @@
     </row>
     <row r="1815" spans="1:18">
       <c r="A1815" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1815" t="s">
         <v>22</v>
       </c>
       <c r="C1815" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1815" t="s">
         <v>22</v>
@@ -102738,13 +102554,13 @@
     </row>
     <row r="1816" spans="1:18">
       <c r="A1816" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1816" t="s">
         <v>22</v>
       </c>
       <c r="C1816" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1816" t="s">
         <v>22</v>
@@ -102794,13 +102610,13 @@
     </row>
     <row r="1817" spans="1:18">
       <c r="A1817" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1817" t="s">
         <v>22</v>
       </c>
       <c r="C1817" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1817" t="s">
         <v>22</v>
@@ -102850,13 +102666,13 @@
     </row>
     <row r="1818" spans="1:18">
       <c r="A1818" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1818" t="s">
         <v>22</v>
       </c>
       <c r="C1818" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1818" t="s">
         <v>22</v>
@@ -102906,13 +102722,13 @@
     </row>
     <row r="1819" spans="1:18">
       <c r="A1819" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1819" t="s">
         <v>22</v>
       </c>
       <c r="C1819" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1819" t="s">
         <v>22</v>
@@ -102962,13 +102778,13 @@
     </row>
     <row r="1820" spans="1:18">
       <c r="A1820" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1820" t="s">
         <v>22</v>
       </c>
       <c r="C1820" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1820" t="s">
         <v>22</v>
@@ -103018,13 +102834,13 @@
     </row>
     <row r="1821" spans="1:18">
       <c r="A1821" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1821" t="s">
         <v>22</v>
       </c>
       <c r="C1821" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1821" t="s">
         <v>22</v>
@@ -103074,13 +102890,13 @@
     </row>
     <row r="1822" spans="1:18">
       <c r="A1822" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1822" t="s">
         <v>22</v>
       </c>
       <c r="C1822" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1822" t="s">
         <v>22</v>
@@ -103130,13 +102946,13 @@
     </row>
     <row r="1823" spans="1:18">
       <c r="A1823" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B1823" t="s">
         <v>22</v>
       </c>
       <c r="C1823" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D1823" t="s">
         <v>22</v>
@@ -103186,19 +103002,19 @@
     </row>
     <row r="1824" spans="1:18">
       <c r="A1824" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1824" t="s">
         <v>22</v>
       </c>
       <c r="C1824" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1824" t="s">
         <v>22</v>
       </c>
       <c r="E1824" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="F1824" t="s">
         <v>22</v>
@@ -103242,19 +103058,19 @@
     </row>
     <row r="1825" spans="1:18">
       <c r="A1825" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1825" t="s">
         <v>22</v>
       </c>
       <c r="C1825" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1825" t="s">
         <v>22</v>
       </c>
       <c r="E1825" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="F1825" t="s">
         <v>22</v>
@@ -103298,19 +103114,19 @@
     </row>
     <row r="1826" spans="1:18">
       <c r="A1826" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1826" t="s">
         <v>22</v>
       </c>
       <c r="C1826" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1826" t="s">
         <v>22</v>
       </c>
       <c r="E1826" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="F1826" t="s">
         <v>22</v>
@@ -103354,19 +103170,19 @@
     </row>
     <row r="1827" spans="1:18">
       <c r="A1827" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1827" t="s">
         <v>22</v>
       </c>
       <c r="C1827" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1827" t="s">
         <v>22</v>
       </c>
       <c r="E1827" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="F1827" t="s">
         <v>22</v>
@@ -103410,19 +103226,19 @@
     </row>
     <row r="1828" spans="1:18">
       <c r="A1828" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1828" t="s">
         <v>22</v>
       </c>
       <c r="C1828" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1828" t="s">
         <v>22</v>
       </c>
       <c r="E1828" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="F1828" t="s">
         <v>22</v>
@@ -103466,19 +103282,19 @@
     </row>
     <row r="1829" spans="1:18">
       <c r="A1829" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1829" t="s">
         <v>22</v>
       </c>
       <c r="C1829" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1829" t="s">
         <v>22</v>
       </c>
       <c r="E1829" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="F1829" t="s">
         <v>22</v>
@@ -103522,13 +103338,13 @@
     </row>
     <row r="1830" spans="1:18">
       <c r="A1830" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1830" t="s">
         <v>22</v>
       </c>
       <c r="C1830" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1830" t="s">
         <v>22</v>
@@ -103578,13 +103394,13 @@
     </row>
     <row r="1831" spans="1:18">
       <c r="A1831" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1831" t="s">
         <v>22</v>
       </c>
       <c r="C1831" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1831" t="s">
         <v>22</v>
@@ -103634,13 +103450,13 @@
     </row>
     <row r="1832" spans="1:18">
       <c r="A1832" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1832" t="s">
         <v>22</v>
       </c>
       <c r="C1832" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1832" t="s">
         <v>22</v>
@@ -103690,13 +103506,13 @@
     </row>
     <row r="1833" spans="1:18">
       <c r="A1833" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1833" t="s">
         <v>22</v>
       </c>
       <c r="C1833" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1833" t="s">
         <v>22</v>
@@ -103714,7 +103530,7 @@
         <v>22</v>
       </c>
       <c r="I1833" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="J1833" t="s">
         <v>22</v>
@@ -103746,13 +103562,13 @@
     </row>
     <row r="1834" spans="1:18">
       <c r="A1834" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1834" t="s">
         <v>22</v>
       </c>
       <c r="C1834" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1834" t="s">
         <v>22</v>
@@ -103770,7 +103586,7 @@
         <v>22</v>
       </c>
       <c r="I1834" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="J1834" t="s">
         <v>22</v>
@@ -103802,13 +103618,13 @@
     </row>
     <row r="1835" spans="1:18">
       <c r="A1835" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1835" t="s">
         <v>22</v>
       </c>
       <c r="C1835" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1835" t="s">
         <v>22</v>
@@ -103826,7 +103642,7 @@
         <v>22</v>
       </c>
       <c r="I1835" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="J1835" t="s">
         <v>22</v>
@@ -103858,13 +103674,13 @@
     </row>
     <row r="1836" spans="1:18">
       <c r="A1836" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1836" t="s">
         <v>22</v>
       </c>
       <c r="C1836" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1836" t="s">
         <v>22</v>
@@ -103882,7 +103698,7 @@
         <v>22</v>
       </c>
       <c r="I1836" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="J1836" t="s">
         <v>22</v>
@@ -103914,13 +103730,13 @@
     </row>
     <row r="1837" spans="1:18">
       <c r="A1837" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1837" t="s">
         <v>22</v>
       </c>
       <c r="C1837" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1837" t="s">
         <v>22</v>
@@ -103938,7 +103754,7 @@
         <v>22</v>
       </c>
       <c r="I1837" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="J1837" t="s">
         <v>22</v>
@@ -103970,13 +103786,13 @@
     </row>
     <row r="1838" spans="1:18">
       <c r="A1838" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B1838" t="s">
         <v>22</v>
       </c>
       <c r="C1838" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D1838" t="s">
         <v>22</v>
@@ -103994,7 +103810,7 @@
         <v>22</v>
       </c>
       <c r="I1838" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="J1838" t="s">
         <v>22</v>
@@ -104026,13 +103842,13 @@
     </row>
     <row r="1839" spans="1:18">
       <c r="A1839" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B1839" t="s">
         <v>22</v>
       </c>
       <c r="C1839" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D1839" t="s">
         <v>22</v>
@@ -104082,19 +103898,19 @@
     </row>
     <row r="1840" spans="1:18">
       <c r="A1840" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B1840" t="s">
         <v>22</v>
       </c>
       <c r="C1840" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D1840" t="s">
         <v>22</v>
       </c>
       <c r="E1840" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="F1840" t="s">
         <v>22</v>
@@ -104138,13 +103954,13 @@
     </row>
     <row r="1841" spans="1:18">
       <c r="A1841" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B1841" t="s">
         <v>22</v>
       </c>
       <c r="C1841" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D1841" t="s">
         <v>22</v>
